--- a/tables/state_variables.xlsx
+++ b/tables/state_variables.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Velocities simulated by the hydrodynamic model, subject to boundary forcing</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href='hydrodynamics.html'&gt;Chapter 7&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href='hydrodynamics.html'&gt;Chapter 10&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">T</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">Incident light attenuated as a function of depth</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href='light-climate.html'&gt;Chapter 13&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href='light-climate.html'&gt;Chapter 16&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">K_d</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">Impacted by photosynthesis, organic decomposition, nitrification, surface exchange, and sediment oxygen demand</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href='bgc-model.html'&gt;Chapter 11&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href='bgc-model.html'&gt;Chapter 14&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">RSi</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">Benthic photosynthesis and respiration</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href='bgc-model.html'&gt;Chapter 11&lt;/a&gt;; &lt;a href='benthic.html'&gt;Chapter 14&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href='bgc-model.html'&gt;Chapter 14&lt;/a&gt;; &lt;a href='benthic.html'&gt;Chapter 17&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">MAC_A</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">Benthic photosynthesis, nutrient uptake, respiration</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href='benthic.html'&gt;Chapter 14&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href='benthic.html'&gt;Chapter 17&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">MAC_B</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">Composite index based on light, temperature, substrate, wave stress, current stress</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href='habitat.html'&gt;Chapter 15&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href='habitat.html'&gt;Chapter 18&lt;/a&gt;</t>
   </si>
 </sst>
 </file>

--- a/tables/state_variables.xlsx
+++ b/tables/state_variables.xlsx
@@ -1,415 +1,470 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_VM/redl/tables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D84EB6F-1965-B146-B7F0-3C7739B2467B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="5360" yWindow="4640" windowWidth="32940" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="state_variables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="state_variables" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
-  <si>
-    <t xml:space="preserve">Table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abbreviation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StateVars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physical variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U, V, W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current velocity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velocities simulated by the hydrodynamic model, subject to boundary forcing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href='hydrodynamics.html'&gt;Chapter 10&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">^{\circ}C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature dynamics subject to surface heating and cooling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">psu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salinity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salinity dynamics subject to inputs, rainfall dilution and evapo-concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\mu S\: cm^{-1}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical conductivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derived from salinity variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Light variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I_{PAR}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\mu E\: m^{-2}\: s^{-1}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAR light intensity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incident light attenuated as a function of depth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href='light-climate.html'&gt;Chapter 16&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m^{-1}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAR extinction coefficient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extinction coefficient based on chl-a, organic matter and suspended solids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E_\lambda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W\: m^{-2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spectral light energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Light spectra: incoming surface light and direct/diffuse below-water profiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\kappa_\lambda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bandwidth-specific attenuation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wavelength-specific attenuation through the water column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biogeochemical variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mmol\: O_2\: m^{-3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dissolved oxygen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impacted by photosynthesis, organic decomposition, nitrification, surface exchange, and sediment oxygen demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href='bgc-model.html'&gt;Chapter 14&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mmol\: Si\: m^{-3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reactive silica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algal uptake, sediment flux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mmol\: P\: m^{-3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filterable reactive phosphorus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algal uptake, organic mineralisation, sediment flux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Particulate inorganic phosphorus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adsorption/desorption of/to free FRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH_4^+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mmol\: N\: m^{-3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ammonium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algal uptake, nitrification, organic mineralisation, sediment flux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO_3^-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nitrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algal uptake, nitrification, denitrification, sediment flux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mmol\: C\: m^{-3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dissolved organic carbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineralisation, algal mortality/excretion, photolysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dissolved organic nitrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dissolved organic phosphorus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Particulate organic carbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breakdown, settling, algal mortality/excretion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Particulate organic nitrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Particulate organic phosphorus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total phosphorus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum of all phosphorus state variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total nitrogen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum of all nitrogen state variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planktonic variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY_{mixed}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixed phytoplankton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Photosynthesis, nutrient uptake, respiration, sedimentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY_{pico}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Picophytoplankton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY_{diatom}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diatoms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHY_{dino}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dinoflagellates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCHLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\mu g\: L^{-1}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total chlorophyll-a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum of planktonic algal groups, converted to chlorophyll-a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sediment &amp; Turbidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">g\: SS\: m^{-3}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suspended sediment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sedimentation, resuspension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turbidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NTU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derived from particulate components in suspension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benthic &amp; Habitat variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mmol\: C\: m^{-2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benthic microalgae (MPB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benthic photosynthesis and respiration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href='bgc-model.html'&gt;Chapter 14&lt;/a&gt;; &lt;a href='benthic.html'&gt;Chapter 17&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAC_A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Above-ground seagrass biomass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benthic photosynthesis, nutrient uptake, respiration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href='benthic.html'&gt;Chapter 17&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAC_B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Below-ground seagrass biomass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root growth, respiration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAC_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seagrass seed biomass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Posidonia seagrass habitat suitability index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composite index based on light, temperature, substrate, wave stress, current stress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href='habitat.html'&gt;Chapter 18&lt;/a&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="146">
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Abbreviation</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Common Name</t>
+  </si>
+  <si>
+    <t>Process Description</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>StateVars</t>
+  </si>
+  <si>
+    <t>Physical variables</t>
+  </si>
+  <si>
+    <t>U, V, W</t>
+  </si>
+  <si>
+    <t>m/s</t>
+  </si>
+  <si>
+    <t>Current velocity</t>
+  </si>
+  <si>
+    <t>Velocities simulated by the hydrodynamic model, subject to boundary forcing</t>
+  </si>
+  <si>
+    <t>&lt;a href='hydrodynamics.html'&gt;Chapter 10&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>^{\circ}C</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>Temperature dynamics subject to surface heating and cooling</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>psu</t>
+  </si>
+  <si>
+    <t>Salinity</t>
+  </si>
+  <si>
+    <t>Salinity dynamics subject to inputs, rainfall dilution and evapo-concentration</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>\mu S\: cm^{-1}</t>
+  </si>
+  <si>
+    <t>Electrical conductivity</t>
+  </si>
+  <si>
+    <t>Derived from salinity variable</t>
+  </si>
+  <si>
+    <t>Light variables</t>
+  </si>
+  <si>
+    <t>I_{PAR}</t>
+  </si>
+  <si>
+    <t>\mu E\: m^{-2}\: s^{-1}</t>
+  </si>
+  <si>
+    <t>PAR light intensity</t>
+  </si>
+  <si>
+    <t>Incident light attenuated as a function of depth</t>
+  </si>
+  <si>
+    <t>&lt;a href='light-climate.html'&gt;Chapter 16&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>K_d</t>
+  </si>
+  <si>
+    <t>m^{-1}</t>
+  </si>
+  <si>
+    <t>PAR extinction coefficient</t>
+  </si>
+  <si>
+    <t>Extinction coefficient based on chl-a, organic matter and suspended solids</t>
+  </si>
+  <si>
+    <t>E_\lambda</t>
+  </si>
+  <si>
+    <t>W\: m^{-2}</t>
+  </si>
+  <si>
+    <t>Spectral light energy</t>
+  </si>
+  <si>
+    <t>Light spectra: incoming surface light and direct/diffuse below-water profiles</t>
+  </si>
+  <si>
+    <t>\kappa_\lambda</t>
+  </si>
+  <si>
+    <t>Bandwidth-specific attenuation</t>
+  </si>
+  <si>
+    <t>Wavelength-specific attenuation through the water column</t>
+  </si>
+  <si>
+    <t>Biogeochemical variables</t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
+    <t>mmol\: O_2\: m^{-3}</t>
+  </si>
+  <si>
+    <t>Dissolved oxygen</t>
+  </si>
+  <si>
+    <t>Impacted by photosynthesis, organic decomposition, nitrification, surface exchange, and sediment oxygen demand</t>
+  </si>
+  <si>
+    <t>&lt;a href='bgc-model.html'&gt;Chapter 14&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>RSi</t>
+  </si>
+  <si>
+    <t>mmol\: Si\: m^{-3}</t>
+  </si>
+  <si>
+    <t>Reactive silica</t>
+  </si>
+  <si>
+    <t>Algal uptake, sediment flux</t>
+  </si>
+  <si>
+    <t>FRP</t>
+  </si>
+  <si>
+    <t>mmol\: P\: m^{-3}</t>
+  </si>
+  <si>
+    <t>Filterable reactive phosphorus</t>
+  </si>
+  <si>
+    <t>Algal uptake, organic mineralisation, sediment flux</t>
+  </si>
+  <si>
+    <t>PIP</t>
+  </si>
+  <si>
+    <t>Particulate inorganic phosphorus</t>
+  </si>
+  <si>
+    <t>Adsorption/desorption of/to free FRP</t>
+  </si>
+  <si>
+    <t>NH_4^+</t>
+  </si>
+  <si>
+    <t>mmol\: N\: m^{-3}</t>
+  </si>
+  <si>
+    <t>Ammonium</t>
+  </si>
+  <si>
+    <t>Algal uptake, nitrification, organic mineralisation, sediment flux</t>
+  </si>
+  <si>
+    <t>NO_3^-</t>
+  </si>
+  <si>
+    <t>Nitrate</t>
+  </si>
+  <si>
+    <t>Algal uptake, nitrification, denitrification, sediment flux</t>
+  </si>
+  <si>
+    <t>DOC</t>
+  </si>
+  <si>
+    <t>mmol\: C\: m^{-3}</t>
+  </si>
+  <si>
+    <t>Dissolved organic carbon</t>
+  </si>
+  <si>
+    <t>Mineralisation, algal mortality/excretion, photolysis</t>
+  </si>
+  <si>
+    <t>DON</t>
+  </si>
+  <si>
+    <t>Dissolved organic nitrogen</t>
+  </si>
+  <si>
+    <t>DOP</t>
+  </si>
+  <si>
+    <t>Dissolved organic phosphorus</t>
+  </si>
+  <si>
+    <t>POC</t>
+  </si>
+  <si>
+    <t>Particulate organic carbon</t>
+  </si>
+  <si>
+    <t>Breakdown, settling, algal mortality/excretion</t>
+  </si>
+  <si>
+    <t>PON</t>
+  </si>
+  <si>
+    <t>Particulate organic nitrogen</t>
+  </si>
+  <si>
+    <t>POP</t>
+  </si>
+  <si>
+    <t>Particulate organic phosphorus</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>Total phosphorus</t>
+  </si>
+  <si>
+    <t>Sum of all phosphorus state variables</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>Total nitrogen</t>
+  </si>
+  <si>
+    <t>Sum of all nitrogen state variables</t>
+  </si>
+  <si>
+    <t>Planktonic variables</t>
+  </si>
+  <si>
+    <t>PHY_{mixed}</t>
+  </si>
+  <si>
+    <t>Mixed phytoplankton</t>
+  </si>
+  <si>
+    <t>Photosynthesis, nutrient uptake, respiration, sedimentation</t>
+  </si>
+  <si>
+    <t>PHY_{pico}</t>
+  </si>
+  <si>
+    <t>Picophytoplankton</t>
+  </si>
+  <si>
+    <t>PHY_{diatom}</t>
+  </si>
+  <si>
+    <t>Diatoms</t>
+  </si>
+  <si>
+    <t>PHY_{dino}</t>
+  </si>
+  <si>
+    <t>Dinoflagellates</t>
+  </si>
+  <si>
+    <t>TCHLA</t>
+  </si>
+  <si>
+    <t>\mu g\: L^{-1}</t>
+  </si>
+  <si>
+    <t>Total chlorophyll-a</t>
+  </si>
+  <si>
+    <t>Sum of planktonic algal groups, converted to chlorophyll-a</t>
+  </si>
+  <si>
+    <t>Sediment &amp; Turbidity</t>
+  </si>
+  <si>
+    <t>g\: SS\: m^{-3}</t>
+  </si>
+  <si>
+    <t>Suspended sediment</t>
+  </si>
+  <si>
+    <t>Sedimentation, resuspension</t>
+  </si>
+  <si>
+    <t>Turbidity</t>
+  </si>
+  <si>
+    <t>NTU</t>
+  </si>
+  <si>
+    <t>Benthic &amp; Habitat variables</t>
+  </si>
+  <si>
+    <t>MPB</t>
+  </si>
+  <si>
+    <t>mmol\: C\: m^{-2}</t>
+  </si>
+  <si>
+    <t>Benthic microalgae (MPB)</t>
+  </si>
+  <si>
+    <t>Benthic photosynthesis and respiration</t>
+  </si>
+  <si>
+    <t>&lt;a href='bgc-model.html'&gt;Chapter 14&lt;/a&gt;; &lt;a href='benthic.html'&gt;Chapter 17&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>MAC_A</t>
+  </si>
+  <si>
+    <t>Above-ground seagrass biomass</t>
+  </si>
+  <si>
+    <t>Benthic photosynthesis, nutrient uptake, respiration</t>
+  </si>
+  <si>
+    <t>&lt;a href='benthic.html'&gt;Chapter 17&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>MAC_B</t>
+  </si>
+  <si>
+    <t>Below-ground seagrass biomass</t>
+  </si>
+  <si>
+    <t>Root growth, respiration</t>
+  </si>
+  <si>
+    <t>MAC_F</t>
+  </si>
+  <si>
+    <t>Seagrass seed biomass</t>
+  </si>
+  <si>
+    <t>HSI</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Posidonia seagrass habitat suitability index</t>
+  </si>
+  <si>
+    <t>Composite index based on light, temperature, substrate, wave stress, current stress</t>
+  </si>
+  <si>
+    <t>&lt;a href='habitat.html'&gt;Chapter 18&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>SS_{1:2}</t>
+  </si>
+  <si>
+    <t>SED_{1:N}</t>
+  </si>
+  <si>
+    <t>Sedimentation, resuspension, cohesion, bedload</t>
+  </si>
+  <si>
+    <t>BIV_{suspfeeder}</t>
+  </si>
+  <si>
+    <t>Benthic invertebrate biomass</t>
+  </si>
+  <si>
+    <t>Filtration and ingestion, excretion, egestion, respiration, mortality</t>
+  </si>
+  <si>
+    <t>BMT (2026)</t>
+  </si>
+  <si>
+    <t>ZOO_{predator}</t>
+  </si>
+  <si>
+    <t>ZOO_{grazer}</t>
+  </si>
+  <si>
+    <t>Predatory zooplankton (e.g. copepods)</t>
+  </si>
+  <si>
+    <t>Grazing zooplankton (e.g. cladocerans)</t>
+  </si>
+  <si>
+    <t>Ingestion, nutrient excretion, respiration, egestion</t>
+  </si>
+  <si>
+    <t>&lt;a href='bgc-model.html'&gt;Chapter 12&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>Various porewater and particulate consituents associated with sediment biogeichemsity</t>
+  </si>
+  <si>
+    <t>CANDI</t>
+  </si>
+  <si>
+    <t>various</t>
+  </si>
+  <si>
+    <t>Sediment concentrations (various)</t>
+  </si>
+  <si>
+    <t>Derived from particulate components in suspension (excluding ST SED components)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -445,6 +500,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -726,11 +790,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="89.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="63.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -753,7 +826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -776,7 +849,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -799,7 +872,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -822,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -845,7 +918,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -868,7 +941,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -891,7 +964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -914,7 +987,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -937,7 +1010,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -960,7 +1033,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -983,7 +1056,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1006,7 +1079,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1029,7 +1102,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1052,7 +1125,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1075,7 +1148,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1098,7 +1171,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1121,7 +1194,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1144,7 +1217,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1167,7 +1240,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1190,7 +1263,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1213,7 +1286,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1236,7 +1309,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1259,30 +1332,30 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1290,13 +1363,13 @@
         <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
         <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F25" t="s">
         <v>91</v>
@@ -1305,7 +1378,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1313,13 +1386,13 @@
         <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
         <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F26" t="s">
         <v>91</v>
@@ -1328,7 +1401,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1336,13 +1409,13 @@
         <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
         <v>68</v>
       </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F27" t="s">
         <v>91</v>
@@ -1351,7 +1424,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1359,184 +1432,299 @@
         <v>88</v>
       </c>
       <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
         <v>98</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>99</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E29" t="s">
         <v>100</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" t="s">
         <v>101</v>
       </c>
-      <c r="G28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="G29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
         <v>102</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" t="s">
         <v>103</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E32" t="s">
         <v>104</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F32" t="s">
+        <v>130</v>
+      </c>
+      <c r="G32" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" t="s">
         <v>105</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" t="s">
         <v>106</v>
       </c>
-      <c r="G29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D34" t="s">
         <v>107</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" t="s">
+        <v>145</v>
+      </c>
+      <c r="G34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
         <v>108</v>
       </c>
-      <c r="E30" t="s">
-        <v>107</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="C35" t="s">
         <v>109</v>
       </c>
-      <c r="G30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="D35" t="s">
         <v>110</v>
       </c>
-      <c r="C31" t="s">
+      <c r="E35" t="s">
         <v>111</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F35" t="s">
         <v>112</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G35" t="s">
         <v>113</v>
       </c>
-      <c r="F31" t="s">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" t="s">
         <v>114</v>
       </c>
-      <c r="G31" t="s">
+      <c r="D36" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="F36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" t="s">
         <v>110</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F37" t="s">
+        <v>120</v>
+      </c>
+      <c r="G37" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" t="s">
         <v>116</v>
       </c>
-      <c r="D32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="G38" t="s">
         <v>117</v>
       </c>
-      <c r="F32" t="s">
-        <v>118</v>
-      </c>
-      <c r="G32" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" t="s">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G39" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" t="s">
         <v>110</v>
       </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" t="s">
-        <v>121</v>
-      </c>
-      <c r="F33" t="s">
-        <v>122</v>
-      </c>
-      <c r="G33" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" t="s">
-        <v>124</v>
-      </c>
-      <c r="F34" t="s">
-        <v>118</v>
-      </c>
-      <c r="G34" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" t="s">
-        <v>127</v>
-      </c>
-      <c r="F35" t="s">
-        <v>128</v>
-      </c>
-      <c r="G35" t="s">
-        <v>129</v>
+      <c r="E40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" t="s">
+        <v>133</v>
+      </c>
+      <c r="G40" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/tables/state_variables.xlsx
+++ b/tables/state_variables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_VM/redl/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D84EB6F-1965-B146-B7F0-3C7739B2467B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3778F63-9044-F740-BF57-A005D8CB8EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5360" yWindow="4640" windowWidth="32940" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-42060" yWindow="6200" windowWidth="32940" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="state_variables" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="151">
   <si>
     <t>Table</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Velocities simulated by the hydrodynamic model, subject to boundary forcing</t>
   </si>
   <si>
-    <t>&lt;a href='hydrodynamics.html'&gt;Chapter 10&lt;/a&gt;</t>
-  </si>
-  <si>
     <t>T</t>
   </si>
   <si>
@@ -88,18 +85,6 @@
     <t>Salinity dynamics subject to inputs, rainfall dilution and evapo-concentration</t>
   </si>
   <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>\mu S\: cm^{-1}</t>
-  </si>
-  <si>
-    <t>Electrical conductivity</t>
-  </si>
-  <si>
-    <t>Derived from salinity variable</t>
-  </si>
-  <si>
     <t>Light variables</t>
   </si>
   <si>
@@ -115,9 +100,6 @@
     <t>Incident light attenuated as a function of depth</t>
   </si>
   <si>
-    <t>&lt;a href='light-climate.html'&gt;Chapter 16&lt;/a&gt;</t>
-  </si>
-  <si>
     <t>K_d</t>
   </si>
   <si>
@@ -166,9 +148,6 @@
     <t>Impacted by photosynthesis, organic decomposition, nitrification, surface exchange, and sediment oxygen demand</t>
   </si>
   <si>
-    <t>&lt;a href='bgc-model.html'&gt;Chapter 14&lt;/a&gt;</t>
-  </si>
-  <si>
     <t>RSi</t>
   </si>
   <si>
@@ -253,9 +232,6 @@
     <t>Particulate organic carbon</t>
   </si>
   <si>
-    <t>Breakdown, settling, algal mortality/excretion</t>
-  </si>
-  <si>
     <t>PON</t>
   </si>
   <si>
@@ -358,33 +334,18 @@
     <t>Benthic microalgae (MPB)</t>
   </si>
   <si>
-    <t>Benthic photosynthesis and respiration</t>
-  </si>
-  <si>
-    <t>&lt;a href='bgc-model.html'&gt;Chapter 14&lt;/a&gt;; &lt;a href='benthic.html'&gt;Chapter 17&lt;/a&gt;</t>
-  </si>
-  <si>
     <t>MAC_A</t>
   </si>
   <si>
     <t>Above-ground seagrass biomass</t>
   </si>
   <si>
-    <t>Benthic photosynthesis, nutrient uptake, respiration</t>
-  </si>
-  <si>
-    <t>&lt;a href='benthic.html'&gt;Chapter 17&lt;/a&gt;</t>
-  </si>
-  <si>
     <t>MAC_B</t>
   </si>
   <si>
     <t>Below-ground seagrass biomass</t>
   </si>
   <si>
-    <t>Root growth, respiration</t>
-  </si>
-  <si>
     <t>MAC_F</t>
   </si>
   <si>
@@ -403,9 +364,6 @@
     <t>Composite index based on light, temperature, substrate, wave stress, current stress</t>
   </si>
   <si>
-    <t>&lt;a href='habitat.html'&gt;Chapter 18&lt;/a&gt;</t>
-  </si>
-  <si>
     <t>SS_{1:2}</t>
   </si>
   <si>
@@ -424,9 +382,6 @@
     <t>Filtration and ingestion, excretion, egestion, respiration, mortality</t>
   </si>
   <si>
-    <t>BMT (2026)</t>
-  </si>
-  <si>
     <t>ZOO_{predator}</t>
   </si>
   <si>
@@ -442,12 +397,6 @@
     <t>Ingestion, nutrient excretion, respiration, egestion</t>
   </si>
   <si>
-    <t>&lt;a href='bgc-model.html'&gt;Chapter 12&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>Various porewater and particulate consituents associated with sediment biogeichemsity</t>
-  </si>
-  <si>
     <t>CANDI</t>
   </si>
   <si>
@@ -458,6 +407,72 @@
   </si>
   <si>
     <t>Derived from particulate components in suspension (excluding ST SED components)</t>
+  </si>
+  <si>
+    <t>&lt;a href='bgc-model.html'&gt;Chapter 12&lt;/a&gt;&lt;br/&gt;&lt;b&gt;ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='hydrodynamics.html'&gt;Chapter 9&lt;/a&gt;&lt;br/&gt;&lt;b&gt;HD,ST,WQ,ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>EC, \rho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\mu S\: cm^{-1} ; kg\:m^{-3} </t>
+  </si>
+  <si>
+    <t>Electrical conductivity; Density</t>
+  </si>
+  <si>
+    <t>Derived from salinity and temperature variables</t>
+  </si>
+  <si>
+    <t>&lt;a href='light-climate.html'&gt;Chapter 15&lt;/a&gt;&lt;br/&gt;&lt;b&gt;WQ,ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='light-climate.html'&gt;Chapter 15&lt;/a&gt;&lt;br/&gt;&lt;b&gt;ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='bgc-model.html'&gt;Chapter 13&lt;/a&gt;&lt;br/&gt;&lt;b&gt;WQ,ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='bgc-model.html'&gt;Chapter 13&lt;/a&gt;&lt;br/&gt;&lt;b&gt;ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Refer to BMT (2026)</t>
+  </si>
+  <si>
+    <t>&lt;a href='benthic.html'&gt;Chapter 16&lt;/a&gt;&lt;br/&gt;&lt;b&gt;WQ,ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='bgc-model.html'&gt;Chapter 13&lt;/a&gt;; &lt;a href='benthic.html'&gt;Chapter 16&lt;/a&gt;&lt;br/&gt;&lt;b&gt;WQ,ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='habitat.html'&gt;Chapter 17&lt;/a&gt;&lt;br/&gt;&lt;b&gt;WQ,ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='benthic.html'&gt;Chapter 16&lt;/a&gt;&lt;br/&gt;&lt;b&gt;ECO&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Photosynthesis, nutrient uptake, respiration, sedimentation (ECO includes mixotrophy)</t>
+  </si>
+  <si>
+    <t>Breakdown, settling, algal mortality/excretion, resuspension</t>
+  </si>
+  <si>
+    <t>Benthic photosynthesis and respiration, resuspension, burial</t>
+  </si>
+  <si>
+    <t>Benthic photosynthesis, nutrient uptake, respiration, translocation</t>
+  </si>
+  <si>
+    <t>Root growth, respiration, translocation</t>
+  </si>
+  <si>
+    <t>Fruit development &amp; release</t>
+  </si>
+  <si>
+    <t>Numerous porewater and particulate consituents associated with sediment biogeochemistry</t>
   </si>
 </sst>
 </file>
@@ -846,7 +861,7 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -857,19 +872,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -880,19 +895,19 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -903,19 +918,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -923,22 +938,22 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -946,22 +961,22 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -969,22 +984,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -992,22 +1007,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1015,22 +1030,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1038,22 +1053,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -1061,22 +1076,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -1084,22 +1099,22 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -1107,22 +1122,22 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -1130,22 +1145,22 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1153,22 +1168,22 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1176,22 +1191,22 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1199,22 +1214,22 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1222,22 +1237,22 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -1245,22 +1260,22 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -1268,22 +1283,22 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1291,22 +1306,22 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -1314,22 +1329,22 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -1337,22 +1352,22 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="F24" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G24" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -1360,22 +1375,22 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1383,22 +1398,22 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1406,22 +1421,22 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1429,22 +1444,22 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" t="s">
         <v>88</v>
       </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="G28" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -1452,22 +1467,22 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1475,22 +1490,22 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E30" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" t="s">
         <v>138</v>
-      </c>
-      <c r="F30" t="s">
-        <v>139</v>
-      </c>
-      <c r="G30" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1498,22 +1513,22 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E31" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G31" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -1521,22 +1536,22 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="G32" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -1544,22 +1559,22 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F33" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G33" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -1567,22 +1582,22 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F34" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="G34" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -1590,22 +1605,22 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="G35" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -1613,22 +1628,22 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F36" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="G36" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -1636,22 +1651,22 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F37" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="G37" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -1659,22 +1674,22 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
         <v>108</v>
       </c>
-      <c r="C38" t="s">
-        <v>121</v>
-      </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="F38" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="G38" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -1682,22 +1697,22 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E39" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="F39" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="G39" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -1705,22 +1720,22 @@
         <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E40" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F40" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G40" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
